--- a/Data/Excel/base.xlsx
+++ b/Data/Excel/base.xlsx
@@ -1265,7 +1265,7 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>30200001</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -1300,7 +1300,7 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>30200002</v>
       </c>
       <c r="C6" t="s">
         <v>34</v>
@@ -1335,7 +1335,7 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>30200003</v>
       </c>
       <c r="C7" t="s">
         <v>36</v>
